--- a/testakten/gesellschafterstreit-squeeze-out-kuechenkoenig-paderborn/xlsx/beteiligungsverhaeltnisse_matrix.xlsx
+++ b/testakten/gesellschafterstreit-squeeze-out-kuechenkoenig-paderborn/xlsx/beteiligungsverhaeltnisse_matrix.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -600,6 +600,7 @@
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -793,10 +794,11 @@
     <row r="12" ht="28" customHeight="1">
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>* Komplementär-GmbH: Kein Kapitalanteil (unbeschränkt haftend); Stimmgewicht fiktiv 260.000 EUR von 1.000.000 EUR Gesamtbasis gemäß § 7 GV. Abfindung auf Basis 26% × Ertragswert/Buchwert.</t>
-        </is>
-      </c>
-    </row>
+          <t>* Komplementär-GmbH: Kein Kapitalanteil (unbeschränkt haftend); Stimmgewicht nach Arbeitsstand 260.000 EUR von 1.000.000 EUR Gesamtbasis gemäß § 7 GV. Abfindung auf Basis 26% × Ertragswert/Buchwert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -936,6 +938,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
